--- a/aussendienst/AAA_Duesseldorf_2026_Aussendienst.xlsx
+++ b/aussendienst/AAA_Duesseldorf_2026_Aussendienst.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Optical Bonding</t>
+          <t>Verguss + Verklebung + Dichtung</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Verklebung</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation / E-Mobility Potting</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>Optical Bonding</t>
+          <t>Verklebung + Dichtung + Verguss</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>LED Encapsulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Optical Bonding</t>
+          <t>Verklebung + Dichtung + Verguss</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Verklebung + Dichtung</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation / E-Mobility-nah</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Verklebung</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Verklebung + Dichtung</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation / E-Mobility Potting</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Verklebung + Dichtung</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
-          <t>kein klarer Geschäftsbereich</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Verklebung + Dichtung</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>kein Geschäftsbereich</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>FIPFG/Gasketing/Sealing</t>
+          <t>Dichtung + Verklebung</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>FIPFG/Gasketing</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Verklebung + Dichtung</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>Gasketing/Sealing</t>
+          <t>Dichtung + Verguss</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G54" s="11" t="inlineStr">
         <is>
-          <t>kein Kerngeschäft</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="G56" s="11" t="inlineStr">
         <is>
-          <t>keiner im Kern</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
-          <t>Kabelverarbeitungs-Maschinenbau; Berührung …</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>Gasketing/Sealing</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="G60" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>Gasketing/Sealing</t>
+          <t>Dichtung + Verguss</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation / Gasketing</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>keiner erkennbar</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="G68" s="11" t="inlineStr">
         <is>
-          <t>Optical Bonding / Klebung</t>
+          <t>Verklebung + Verguss</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="G70" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr"/>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Verklebung + Dichtung</t>
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr"/>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>kein klarer Bereich …</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="G74" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Verklebung + Dichtung</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
-          <t>Optical Bonding</t>
+          <t>Verguss + Verklebung + Dichtung</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="G84" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>kein klarer Bereich. KI-Bildverarbeitung für …</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="G90" s="11" t="inlineStr">
         <is>
-          <t>unbekannt</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="G92" s="11" t="inlineStr">
         <is>
-          <t>kein klarer Geschäftsbereich</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="G94" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>keiner eindeutig</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="G96" s="11" t="inlineStr">
         <is>
-          <t>keiner</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H96" s="11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>keiner</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="G98" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Verklebung + Dichtung</t>
         </is>
       </c>
       <c r="H98" s="11" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>kein direkter Bereich; Sekundär: Electrical …</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="G100" s="11" t="inlineStr">
         <is>
-          <t>Gasketing/Sealing</t>
+          <t>Dichtung + Verguss</t>
         </is>
       </c>
       <c r="H100" s="11" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>unbekannt</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="G102" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation / Gasketing</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H102" s="11" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G104" s="11" t="inlineStr">
         <is>
-          <t>nicht bestimmbar</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H104" s="11" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H105" s="8" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H106" s="11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H107" s="8" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="G108" s="11" t="inlineStr">
         <is>
-          <t>kein klarer Bereich erkennbar</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H108" s="11" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H109" s="8" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>Gasketing/Sealing</t>
+          <t>Dichtung + Verguss</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="G112" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H112" s="11" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H113" s="8" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H115" s="8" t="inlineStr"/>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="G116" s="11" t="inlineStr">
         <is>
-          <t>Optical Bonding</t>
+          <t>Verguss + Verklebung + Dichtung</t>
         </is>
       </c>
       <c r="H116" s="11" t="inlineStr"/>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr"/>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="G118" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H118" s="11" t="inlineStr"/>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>unbekannt</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H119" s="8" t="inlineStr"/>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="G120" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Dichtung</t>
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="G122" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Verklebung + Dichtung</t>
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="G124" s="11" t="inlineStr">
         <is>
-          <t>unbekannt</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H124" s="11" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H125" s="8" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="G126" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss + Verklebung + Dichtung</t>
         </is>
       </c>
       <c r="H126" s="11" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>keiner erkennbar</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H127" s="8" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="G128" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H128" s="11" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H129" s="8" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>keiner</t>
+          <t>kein klarer Bereich</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr"/>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Electrical Insulation</t>
+          <t>Verguss</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
@@ -6922,7 +6922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6983,70 +6983,82 @@
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
+          <t>Demak-Bereich</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Verguss = Electrical Insulation / E-Mobility Potting / LED Encapsulation (Vergussmasse, Dosier- und Vergussanlagen). Verklebung = Optical Bonding (Displays/Touch). Dichtung = FIPFG/Gasketing (Schaumdichtung). Mehrere Begriffe: in dieser Reihenfolge nach Bedeutung. Filter: Spalte "Demak-Bereich" nach "Verguss" filtern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
           <t>Nicht ansprechen</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Bestandskunde im CRM oder harter Ausschluss (Wettbewerber, Händler, Fertigung außerhalb).</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr"/>
-      <c r="B8" s="16" t="inlineStr"/>
-    </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr"/>
+      <c r="B9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Belastbarkeit</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Vorläufig</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>Alle Einstufungen beruhen auf Websuche-Treffern. Es gab keinen Browserzugriff und keinen Zugriff auf Patentdatenbanken. Fertigung und Verguss sind aus Sitz und Produkttyp abgeleitet, nicht vor Ort belegt.</t>
-        </is>
-      </c>
+      <c r="B10" s="16" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Für Gespräche</t>
+          <t>Vorläufig</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Verguss/Verklebung nur als Frage formulieren ("in Sensoren stecken typischerweise vergossene Bauteile"), nicht als Tatsache über die Firma.</t>
+          <t>Alle Einstufungen beruhen auf Websuche-Treffern. Es gab keinen Browserzugriff und keinen Zugriff auf Patentdatenbanken. Fertigung und Verguss sind aus Sitz und Produkttyp abgeleitet, nicht vor Ort belegt.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>Patente</t>
+          <t>Für Gespräche</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>Nicht geprüft. Eigenfertigung und Wettbewerbereinsatz im Gespräch erfragen.</t>
+          <t>Verguss/Verklebung nur als Frage formulieren ("in Sensoren stecken typischerweise vergossene Bauteile"), nicht als Tatsache über die Firma.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
+          <t>Patente</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Nicht geprüft. Eigenfertigung und Wettbewerbereinsatz im Gespräch erfragen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
           <t>Messe</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Halle ist in der Ausstellerliste nicht angegeben, nur die Standnummer.</t>
         </is>
